--- a/04_DESIGN_TABLES/DesignTable_5406C_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5406C_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -824,47 +824,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5406-C-4</t>
+          <t>5406-C-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.92</v>
+        <v>1.25</v>
       </c>
       <c r="C6" t="n">
-        <v>0.43301</v>
+        <v>1.1547</v>
       </c>
       <c r="D6" t="n">
-        <v>0.75</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.43</v>
+        <v>1.48</v>
       </c>
       <c r="F6" t="n">
-        <v>0.67</v>
+        <v>1.16</v>
       </c>
       <c r="G6" t="n">
-        <v>0.43</v>
+        <v>1.48</v>
       </c>
       <c r="H6" t="n">
-        <v>0.67</v>
+        <v>1.16</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0556</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.215</v>
+        <v>0.74</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2594</v>
+        <v>0.8096</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5406-C-4</t>
+          <t>5406-C-20</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Female Pipe Cap (NPTF), 1/4-18 NPTF (female)</t>
+          <t>Female Pipe Cap (NPTF), 1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1/4-18 NPTF (female)</t>
+          <t>1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -889,87 +889,169 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Air-Way s87 only (double-pass 6 rows); female NPTF per ANSI B1.20.3 | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 STEP VERIFIED -08 only), helical thread over P1; closed hex cap, hex over the full length (ASSUMPTION - cap crown shape unpublished), end chamfers NOT modelled</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p67 table TFA-p067-t01 "5406-C PIPE CAP" row 5406-C-20 col "L LGTH" = "1.250" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 57.5, page verified) [Brennan = yes 2026-10-18] - overall cap length; mapping: TFA p66 5406-C drawing: L = whole closed cap, C HEX = cap hex (impact/F2b.json, certain role; Air-Way caps of the other sizes differ, 0/6); same-table check on today's base: 0/6 rows with an Air-Way/OMi value agree with this catalog column to rounding (6 differ, e.g. 5406-C-02 0.69 vs 0.563); C1HEX@HEX: Brennan TFA catalog p67 table TFA-p067-t01 "5406-C PIPE CAP" row 5406-C-20 col "C HEX" = "2.000" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 57.5, page verified) [Brennan = yes 2026-10-18] - cap hex; mapping: TFA p66 5406-C drawing: L = whole closed cap, C HEX = cap hex (impact/F2b.json, certain role; Air-Way caps of the other sizes differ, 0/6); same-table check on today's base: 3/6 rows with an Air-Way/OMi value agree with this catalog column to rounding (3 differ, e.g. 5406-C-06 0.88 vs 0.812); TAPDRILL@BORE: end library gen_straight2 FPT[20] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 1.48, FPT_P1 1.16 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A@DRIVE: end library: ASME B1.20.1 / B1.20.3 1-1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[20] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; $PRP@Threads: thread text from the part-number dash, format of the built 5406C rows | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 STEP VERIFIED -08 only), helical thread over P1; closed hex cap, hex over the full length (ASSUMPTION - cap crown shape unpublished), end chamfers NOT modelled</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex from the Brennan TFA catalog p67 alone (Brennan caps are 0.11-0.36 shorter than the Air-Way caps built in this table); end wall L - P1 = 0.09</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>5406-C-04</t>
+          <t>5406-C-20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5406-C-6</t>
+          <t>5406-C-4</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="C7" t="n">
-        <v>0.50807</v>
+        <v>0.43301</v>
       </c>
       <c r="D7" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="E7" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="F7" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="G7" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="H7" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="I7" t="n">
         <v>0.0556</v>
       </c>
       <c r="J7" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2594</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5406-C-4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Female Pipe Cap (NPTF), 1/4-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5406C</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>plug head</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Air-Way s87 only (double-pass 6 rows); female NPTF per ANSI B1.20.3 | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 STEP VERIFIED -08 only), helical thread over P1; closed hex cap, hex over the full length (ASSUMPTION - cap crown shape unpublished), end chamfers NOT modelled</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>5406-C-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5406-C-6</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.50807</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.285</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>0.3294</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>5406-C-6</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Female Pipe Cap (NPTF), 3/8-18 NPTF (female)</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5406C</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>3/8-18 NPTF (female)</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>plug head</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Air-Way s87 only (double-pass 6 rows); female NPTF per ANSI B1.20.3 | MODEL: female NPTF port: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table; Brennan 5405-08-08 STEP VERIFIED -08 only), helical thread over P1; closed hex cap, hex over the full length (ASSUMPTION - cap crown shape unpublished), end chamfers NOT modelled</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>5406-C-06</t>
         </is>
